--- a/results/reporte_poisson.xlsx
+++ b/results/reporte_poisson.xlsx
@@ -199,7 +199,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -259,11 +259,14 @@
     <xf numFmtId="164" fontId="10" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -481,7 +484,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>98</row>
+      <row>116</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5905500" cy="3429000"/>
@@ -506,7 +509,7 @@
     <from>
       <col>11</col>
       <colOff>0</colOff>
-      <row>98</row>
+      <row>116</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5905500" cy="3429000"/>
@@ -4535,7 +4538,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L95"/>
+  <dimension ref="A1:L113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -5626,35 +5629,29 @@
       <c r="E56" s="6" t="n">
         <v>66772.91800000001</v>
       </c>
-      <c r="F56" s="6" t="n">
-        <v>137806.737</v>
+      <c r="F56" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="57" ht="16" customHeight="1">
       <c r="A57" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B57" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C57" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D57" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E57" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F57" s="21" t="inlineStr">
+      <c r="B57" s="7" t="n">
+        <v>283.815</v>
+      </c>
+      <c r="C57" s="7" t="n">
+        <v>1161.403</v>
+      </c>
+      <c r="D57" s="7" t="n">
+        <v>10088.374</v>
+      </c>
+      <c r="E57" s="7" t="n">
+        <v>57658.142</v>
+      </c>
+      <c r="F57" s="22" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -5664,27 +5661,19 @@
       <c r="A58" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B58" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C58" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D58" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E58" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F58" s="22" t="inlineStr">
+      <c r="B58" s="6" t="n">
+        <v>254.485</v>
+      </c>
+      <c r="C58" s="6" t="n">
+        <v>1187.386</v>
+      </c>
+      <c r="D58" s="6" t="n">
+        <v>10578.748</v>
+      </c>
+      <c r="E58" s="6" t="n">
+        <v>51839.525</v>
+      </c>
+      <c r="F58" s="21" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -5694,27 +5683,19 @@
       <c r="A59" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="B59" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C59" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D59" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E59" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F59" s="21" t="inlineStr">
+      <c r="B59" s="7" t="n">
+        <v>261.036</v>
+      </c>
+      <c r="C59" s="7" t="n">
+        <v>1016.967</v>
+      </c>
+      <c r="D59" s="7" t="n">
+        <v>10405.703</v>
+      </c>
+      <c r="E59" s="7" t="n">
+        <v>47730.736</v>
+      </c>
+      <c r="F59" s="22" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -5724,27 +5705,19 @@
       <c r="A60" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="B60" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C60" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D60" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E60" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F60" s="22" t="inlineStr">
+      <c r="B60" s="6" t="n">
+        <v>248.115</v>
+      </c>
+      <c r="C60" s="6" t="n">
+        <v>1028.491</v>
+      </c>
+      <c r="D60" s="6" t="n">
+        <v>10470.363</v>
+      </c>
+      <c r="E60" s="6" t="n">
+        <v>51954.916</v>
+      </c>
+      <c r="F60" s="21" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -5754,27 +5727,19 @@
       <c r="A61" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="B61" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C61" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D61" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E61" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F61" s="21" t="inlineStr">
+      <c r="B61" s="7" t="n">
+        <v>256.771</v>
+      </c>
+      <c r="C61" s="7" t="n">
+        <v>1100.745</v>
+      </c>
+      <c r="D61" s="7" t="n">
+        <v>11114.013</v>
+      </c>
+      <c r="E61" s="7" t="n">
+        <v>53032.826</v>
+      </c>
+      <c r="F61" s="22" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -5784,27 +5749,19 @@
       <c r="A62" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="B62" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C62" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D62" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E62" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F62" s="22" t="inlineStr">
+      <c r="B62" s="6" t="n">
+        <v>269.905</v>
+      </c>
+      <c r="C62" s="6" t="n">
+        <v>1141.019</v>
+      </c>
+      <c r="D62" s="6" t="n">
+        <v>10571.046</v>
+      </c>
+      <c r="E62" s="6" t="n">
+        <v>52808.613</v>
+      </c>
+      <c r="F62" s="21" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -5814,27 +5771,19 @@
       <c r="A63" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="B63" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C63" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D63" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E63" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F63" s="21" t="inlineStr">
+      <c r="B63" s="7" t="n">
+        <v>247.72</v>
+      </c>
+      <c r="C63" s="7" t="n">
+        <v>1097.421</v>
+      </c>
+      <c r="D63" s="7" t="n">
+        <v>10742.955</v>
+      </c>
+      <c r="E63" s="7" t="n">
+        <v>52088.145</v>
+      </c>
+      <c r="F63" s="22" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -5844,27 +5793,19 @@
       <c r="A64" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="B64" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C64" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D64" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E64" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F64" s="22" t="inlineStr">
+      <c r="B64" s="6" t="n">
+        <v>245.667</v>
+      </c>
+      <c r="C64" s="6" t="n">
+        <v>970.279</v>
+      </c>
+      <c r="D64" s="6" t="n">
+        <v>10542.42</v>
+      </c>
+      <c r="E64" s="6" t="n">
+        <v>49781.896</v>
+      </c>
+      <c r="F64" s="21" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -5874,27 +5815,19 @@
       <c r="A65" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="B65" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C65" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D65" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E65" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F65" s="21" t="inlineStr">
+      <c r="B65" s="7" t="n">
+        <v>264.814</v>
+      </c>
+      <c r="C65" s="7" t="n">
+        <v>987.454</v>
+      </c>
+      <c r="D65" s="7" t="n">
+        <v>10293.134</v>
+      </c>
+      <c r="E65" s="7" t="n">
+        <v>50434.82</v>
+      </c>
+      <c r="F65" s="22" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -5907,19 +5840,21 @@
         </is>
       </c>
       <c r="B66" s="9" t="n">
-        <v>294.936</v>
+        <v>262.726</v>
       </c>
       <c r="C66" s="9" t="n">
-        <v>1195.328</v>
+        <v>1088.649</v>
       </c>
       <c r="D66" s="9" t="n">
-        <v>11220.918</v>
+        <v>10602.767</v>
       </c>
       <c r="E66" s="9" t="n">
-        <v>66772.91800000001</v>
-      </c>
-      <c r="F66" s="9" t="n">
-        <v>137806.737</v>
+        <v>53410.254</v>
+      </c>
+      <c r="F66" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="67" ht="16" customHeight="1">
@@ -5929,19 +5864,21 @@
         </is>
       </c>
       <c r="B67" s="10" t="n">
-        <v>0</v>
+        <v>15.408</v>
       </c>
       <c r="C67" s="10" t="n">
-        <v>0</v>
+        <v>78.992</v>
       </c>
       <c r="D67" s="10" t="n">
-        <v>0</v>
+        <v>329.424</v>
       </c>
       <c r="E67" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F67" s="10" t="n">
-        <v>0</v>
+        <v>5076.594</v>
+      </c>
+      <c r="F67" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="68" ht="16" customHeight="1">
@@ -5951,19 +5888,21 @@
         </is>
       </c>
       <c r="B68" s="11" t="n">
-        <v>0</v>
+        <v>5.86</v>
       </c>
       <c r="C68" s="11" t="n">
-        <v>0</v>
+        <v>7.26</v>
       </c>
       <c r="D68" s="11" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="E68" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F68" s="11" t="n">
-        <v>0</v>
+        <v>9.5</v>
+      </c>
+      <c r="F68" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="69" ht="16" customHeight="1">
@@ -5973,19 +5912,21 @@
         </is>
       </c>
       <c r="B69" s="12" t="n">
-        <v>72093</v>
+        <v>70733</v>
       </c>
       <c r="C69" s="12" t="n">
-        <v>305050</v>
+        <v>300590</v>
       </c>
       <c r="D69" s="12" t="n">
-        <v>2479060</v>
+        <v>2573935</v>
       </c>
       <c r="E69" s="12" t="n">
-        <v>7904234</v>
-      </c>
-      <c r="F69" s="12" t="n">
-        <v>12127661</v>
+        <v>6751089</v>
+      </c>
+      <c r="F69" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="70" ht="6" customHeight="1">
@@ -6040,19 +5981,21 @@
         <v>1</v>
       </c>
       <c r="B73" s="6" t="n">
-        <v>293.926</v>
+        <v>425.559</v>
       </c>
       <c r="C73" s="6" t="n">
-        <v>1194.348</v>
+        <v>1998.938</v>
       </c>
       <c r="D73" s="6" t="n">
-        <v>11221.118</v>
+        <v>15910.887</v>
       </c>
       <c r="E73" s="6" t="n">
-        <v>66773.118</v>
-      </c>
-      <c r="F73" s="6" t="n">
-        <v>137805.257</v>
+        <v>86719.504</v>
+      </c>
+      <c r="F73" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="74" ht="16" customHeight="1">
@@ -6060,19 +6003,21 @@
         <v>2</v>
       </c>
       <c r="B74" s="7" t="n">
-        <v>294.126</v>
+        <v>465.797</v>
       </c>
       <c r="C74" s="7" t="n">
-        <v>1135.128</v>
+        <v>1862.22</v>
       </c>
       <c r="D74" s="7" t="n">
-        <v>11210.118</v>
+        <v>15491.049</v>
       </c>
       <c r="E74" s="7" t="n">
-        <v>66774.228</v>
-      </c>
-      <c r="F74" s="7" t="n">
-        <v>137815.137</v>
+        <v>73890.344</v>
+      </c>
+      <c r="F74" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="75" ht="16" customHeight="1">
@@ -6080,19 +6025,21 @@
         <v>3</v>
       </c>
       <c r="B75" s="6" t="n">
-        <v>294.136</v>
+        <v>406.269</v>
       </c>
       <c r="C75" s="6" t="n">
-        <v>1196.328</v>
+        <v>2217.005</v>
       </c>
       <c r="D75" s="6" t="n">
-        <v>11211.118</v>
+        <v>17011.323</v>
       </c>
       <c r="E75" s="6" t="n">
-        <v>66773.41800000001</v>
-      </c>
-      <c r="F75" s="6" t="n">
-        <v>137806.457</v>
+        <v>89812.246</v>
+      </c>
+      <c r="F75" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="76" ht="16" customHeight="1">
@@ -6100,46 +6047,40 @@
         <v>4</v>
       </c>
       <c r="B76" s="7" t="n">
-        <v>294.332</v>
+        <v>451.819</v>
       </c>
       <c r="C76" s="7" t="n">
-        <v>1195.218</v>
+        <v>2224.23</v>
       </c>
       <c r="D76" s="7" t="n">
-        <v>11219.819</v>
+        <v>15935.354</v>
       </c>
       <c r="E76" s="7" t="n">
-        <v>66771.91800000001</v>
-      </c>
-      <c r="F76" s="7" t="n">
-        <v>137815.737</v>
+        <v>96359.06</v>
+      </c>
+      <c r="F76" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="77" ht="16" customHeight="1">
       <c r="A77" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="B77" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C77" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D77" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E77" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F77" s="22" t="inlineStr">
+      <c r="B77" s="6" t="n">
+        <v>490.776</v>
+      </c>
+      <c r="C77" s="6" t="n">
+        <v>2218.694</v>
+      </c>
+      <c r="D77" s="6" t="n">
+        <v>16694.387</v>
+      </c>
+      <c r="E77" s="6" t="n">
+        <v>97835.363</v>
+      </c>
+      <c r="F77" s="21" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -6149,27 +6090,19 @@
       <c r="A78" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="B78" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C78" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D78" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E78" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F78" s="21" t="inlineStr">
+      <c r="B78" s="7" t="n">
+        <v>509.15</v>
+      </c>
+      <c r="C78" s="7" t="n">
+        <v>2176.21</v>
+      </c>
+      <c r="D78" s="7" t="n">
+        <v>18328.084</v>
+      </c>
+      <c r="E78" s="7" t="n">
+        <v>97220.106</v>
+      </c>
+      <c r="F78" s="22" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -6179,27 +6112,19 @@
       <c r="A79" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="B79" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C79" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D79" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E79" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F79" s="22" t="inlineStr">
+      <c r="B79" s="6" t="n">
+        <v>550.375</v>
+      </c>
+      <c r="C79" s="6" t="n">
+        <v>2070.998</v>
+      </c>
+      <c r="D79" s="6" t="n">
+        <v>17922.875</v>
+      </c>
+      <c r="E79" s="6" t="n">
+        <v>116670.638</v>
+      </c>
+      <c r="F79" s="21" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -6209,27 +6134,19 @@
       <c r="A80" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="B80" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C80" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D80" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E80" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F80" s="21" t="inlineStr">
+      <c r="B80" s="7" t="n">
+        <v>538.732</v>
+      </c>
+      <c r="C80" s="7" t="n">
+        <v>2283.96</v>
+      </c>
+      <c r="D80" s="7" t="n">
+        <v>18710.304</v>
+      </c>
+      <c r="E80" s="7" t="n">
+        <v>99477.42200000001</v>
+      </c>
+      <c r="F80" s="22" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -6239,27 +6156,19 @@
       <c r="A81" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="B81" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C81" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D81" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E81" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F81" s="22" t="inlineStr">
+      <c r="B81" s="6" t="n">
+        <v>501.71</v>
+      </c>
+      <c r="C81" s="6" t="n">
+        <v>2335.755</v>
+      </c>
+      <c r="D81" s="6" t="n">
+        <v>18544.987</v>
+      </c>
+      <c r="E81" s="6" t="n">
+        <v>93597.995</v>
+      </c>
+      <c r="F81" s="21" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -6269,27 +6178,19 @@
       <c r="A82" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="B82" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C82" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D82" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E82" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F82" s="21" t="inlineStr">
+      <c r="B82" s="7" t="n">
+        <v>562.484</v>
+      </c>
+      <c r="C82" s="7" t="n">
+        <v>2044.42</v>
+      </c>
+      <c r="D82" s="7" t="n">
+        <v>16494.355</v>
+      </c>
+      <c r="E82" s="7" t="n">
+        <v>116166.658</v>
+      </c>
+      <c r="F82" s="22" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -6302,19 +6203,21 @@
         </is>
       </c>
       <c r="B83" s="9" t="n">
-        <v>294.13</v>
+        <v>490.267</v>
       </c>
       <c r="C83" s="9" t="n">
-        <v>1180.255</v>
+        <v>2143.243</v>
       </c>
       <c r="D83" s="9" t="n">
-        <v>11215.543</v>
+        <v>17104.361</v>
       </c>
       <c r="E83" s="9" t="n">
-        <v>66773.171</v>
-      </c>
-      <c r="F83" s="9" t="n">
-        <v>137810.647</v>
+        <v>96774.93399999999</v>
+      </c>
+      <c r="F83" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="84" ht="16" customHeight="1">
@@ -6324,19 +6227,21 @@
         </is>
       </c>
       <c r="B84" s="10" t="n">
-        <v>0.144</v>
+        <v>49.985</v>
       </c>
       <c r="C84" s="10" t="n">
-        <v>26.064</v>
+        <v>137.994</v>
       </c>
       <c r="D84" s="10" t="n">
-        <v>4.959</v>
+        <v>1129.801</v>
       </c>
       <c r="E84" s="10" t="n">
-        <v>0.829</v>
-      </c>
-      <c r="F84" s="10" t="n">
-        <v>4.813</v>
+        <v>12099.856</v>
+      </c>
+      <c r="F84" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="85" ht="16" customHeight="1">
@@ -6346,19 +6251,21 @@
         </is>
       </c>
       <c r="B85" s="11" t="n">
-        <v>0.05</v>
+        <v>10.2</v>
       </c>
       <c r="C85" s="11" t="n">
-        <v>2.21</v>
+        <v>6.44</v>
       </c>
       <c r="D85" s="11" t="n">
-        <v>0.04</v>
+        <v>6.61</v>
       </c>
       <c r="E85" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F85" s="11" t="n">
-        <v>0</v>
+        <v>12.5</v>
+      </c>
+      <c r="F85" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="86" ht="16" customHeight="1">
@@ -6368,313 +6275,732 @@
         </is>
       </c>
       <c r="B86" s="12" t="n">
-        <v>72093</v>
+        <v>71747</v>
       </c>
       <c r="C86" s="12" t="n">
-        <v>305050</v>
+        <v>310660</v>
       </c>
       <c r="D86" s="12" t="n">
-        <v>2479060</v>
+        <v>2317058</v>
       </c>
       <c r="E86" s="12" t="n">
-        <v>7904234</v>
-      </c>
-      <c r="F86" s="12" t="n">
-        <v>12127661</v>
-      </c>
-    </row>
-    <row r="89" ht="20" customHeight="1">
-      <c r="A89" s="2" t="inlineStr">
+        <v>11664547</v>
+      </c>
+      <c r="F86" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="6" customHeight="1">
+      <c r="A87" s="13" t="n"/>
+      <c r="B87" s="13" t="n"/>
+      <c r="C87" s="13" t="n"/>
+      <c r="D87" s="13" t="n"/>
+      <c r="E87" s="13" t="n"/>
+      <c r="F87" s="13" t="n"/>
+    </row>
+    <row r="88" ht="20" customHeight="1">
+      <c r="A88" s="3" t="inlineStr">
+        <is>
+          <t>Procesos fork (12 procesos)</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="18" customHeight="1">
+      <c r="A89" s="4" t="inlineStr">
+        <is>
+          <t>Rep</t>
+        </is>
+      </c>
+      <c r="B89" s="4" t="inlineStr">
+        <is>
+          <t>N = 100</t>
+        </is>
+      </c>
+      <c r="C89" s="4" t="inlineStr">
+        <is>
+          <t>N = 200</t>
+        </is>
+      </c>
+      <c r="D89" s="4" t="inlineStr">
+        <is>
+          <t>N = 500</t>
+        </is>
+      </c>
+      <c r="E89" s="4" t="inlineStr">
+        <is>
+          <t>N = 1K</t>
+        </is>
+      </c>
+      <c r="F89" s="4" t="inlineStr">
+        <is>
+          <t>N = 2K</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="16" customHeight="1">
+      <c r="A90" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B90" s="6" t="n">
+        <v>795.912</v>
+      </c>
+      <c r="C90" s="6" t="n">
+        <v>3070.911</v>
+      </c>
+      <c r="D90" s="6" t="n">
+        <v>23955.298</v>
+      </c>
+      <c r="E90" s="6" t="n">
+        <v>114413.125</v>
+      </c>
+      <c r="F90" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="16" customHeight="1">
+      <c r="A91" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B91" s="7" t="n">
+        <v>724.09</v>
+      </c>
+      <c r="C91" s="7" t="n">
+        <v>3185.604</v>
+      </c>
+      <c r="D91" s="7" t="n">
+        <v>22581.335</v>
+      </c>
+      <c r="E91" s="7" t="n">
+        <v>112752.926</v>
+      </c>
+      <c r="F91" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="16" customHeight="1">
+      <c r="A92" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B92" s="6" t="n">
+        <v>777.981</v>
+      </c>
+      <c r="C92" s="6" t="n">
+        <v>3280.217</v>
+      </c>
+      <c r="D92" s="6" t="n">
+        <v>24358.039</v>
+      </c>
+      <c r="E92" s="6" t="n">
+        <v>123514.787</v>
+      </c>
+      <c r="F92" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="16" customHeight="1">
+      <c r="A93" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B93" s="7" t="n">
+        <v>777.574</v>
+      </c>
+      <c r="C93" s="7" t="n">
+        <v>2892.879</v>
+      </c>
+      <c r="D93" s="7" t="n">
+        <v>21933.515</v>
+      </c>
+      <c r="E93" s="7" t="n">
+        <v>143253.147</v>
+      </c>
+      <c r="F93" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="16" customHeight="1">
+      <c r="A94" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B94" s="6" t="n">
+        <v>774.697</v>
+      </c>
+      <c r="C94" s="6" t="n">
+        <v>2968.101</v>
+      </c>
+      <c r="D94" s="6" t="n">
+        <v>22369.455</v>
+      </c>
+      <c r="E94" s="6" t="n">
+        <v>124252.036</v>
+      </c>
+      <c r="F94" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="16" customHeight="1">
+      <c r="A95" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B95" s="7" t="n">
+        <v>756.897</v>
+      </c>
+      <c r="C95" s="7" t="n">
+        <v>3202.824</v>
+      </c>
+      <c r="D95" s="7" t="n">
+        <v>24033.051</v>
+      </c>
+      <c r="E95" s="7" t="n">
+        <v>112101.691</v>
+      </c>
+      <c r="F95" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="16" customHeight="1">
+      <c r="A96" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B96" s="6" t="n">
+        <v>765.816</v>
+      </c>
+      <c r="C96" s="6" t="n">
+        <v>3361.423</v>
+      </c>
+      <c r="D96" s="6" t="n">
+        <v>23028.248</v>
+      </c>
+      <c r="E96" s="6" t="n">
+        <v>125928.15</v>
+      </c>
+      <c r="F96" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="16" customHeight="1">
+      <c r="A97" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B97" s="7" t="n">
+        <v>812.193</v>
+      </c>
+      <c r="C97" s="7" t="n">
+        <v>2994.351</v>
+      </c>
+      <c r="D97" s="7" t="n">
+        <v>22556.966</v>
+      </c>
+      <c r="E97" s="7" t="n">
+        <v>108919.229</v>
+      </c>
+      <c r="F97" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="16" customHeight="1">
+      <c r="A98" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B98" s="6" t="n">
+        <v>782.176</v>
+      </c>
+      <c r="C98" s="6" t="n">
+        <v>3157.736</v>
+      </c>
+      <c r="D98" s="6" t="n">
+        <v>27064.323</v>
+      </c>
+      <c r="E98" s="6" t="n">
+        <v>109451.341</v>
+      </c>
+      <c r="F98" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="16" customHeight="1">
+      <c r="A99" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="B99" s="7" t="n">
+        <v>741.16</v>
+      </c>
+      <c r="C99" s="7" t="n">
+        <v>2957.61</v>
+      </c>
+      <c r="D99" s="7" t="n">
+        <v>24436.47</v>
+      </c>
+      <c r="E99" s="7" t="n">
+        <v>107050.923</v>
+      </c>
+      <c r="F99" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="16" customHeight="1">
+      <c r="A100" s="8" t="inlineStr">
+        <is>
+          <t>Promedio</t>
+        </is>
+      </c>
+      <c r="B100" s="9" t="n">
+        <v>770.85</v>
+      </c>
+      <c r="C100" s="9" t="n">
+        <v>3107.166</v>
+      </c>
+      <c r="D100" s="9" t="n">
+        <v>23631.67</v>
+      </c>
+      <c r="E100" s="9" t="n">
+        <v>118163.735</v>
+      </c>
+      <c r="F100" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="16" customHeight="1">
+      <c r="A101" s="8" t="inlineStr">
+        <is>
+          <t>Desv. Est.</t>
+        </is>
+      </c>
+      <c r="B101" s="10" t="n">
+        <v>24.217</v>
+      </c>
+      <c r="C101" s="10" t="n">
+        <v>146.328</v>
+      </c>
+      <c r="D101" s="10" t="n">
+        <v>1425.605</v>
+      </c>
+      <c r="E101" s="10" t="n">
+        <v>10584.987</v>
+      </c>
+      <c r="F101" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="16" customHeight="1">
+      <c r="A102" s="8" t="inlineStr">
+        <is>
+          <t>CV (%)</t>
+        </is>
+      </c>
+      <c r="B102" s="11" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="C102" s="11" t="n">
+        <v>4.71</v>
+      </c>
+      <c r="D102" s="11" t="n">
+        <v>6.03</v>
+      </c>
+      <c r="E102" s="11" t="n">
+        <v>8.960000000000001</v>
+      </c>
+      <c r="F102" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="16" customHeight="1">
+      <c r="A103" s="8" t="inlineStr">
+        <is>
+          <t>Iter. prom.</t>
+        </is>
+      </c>
+      <c r="B103" s="12" t="n">
+        <v>76108</v>
+      </c>
+      <c r="C103" s="12" t="n">
+        <v>303976</v>
+      </c>
+      <c r="D103" s="12" t="n">
+        <v>2185791</v>
+      </c>
+      <c r="E103" s="12" t="n">
+        <v>9777002</v>
+      </c>
+      <c r="F103" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="20" customHeight="1">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>Tabla 2  —  Promedio y Speedup  (ref: serial_std)</t>
         </is>
       </c>
     </row>
-    <row r="90" ht="28" customHeight="1">
-      <c r="A90" s="14" t="inlineStr">
+    <row r="107" ht="28" customHeight="1">
+      <c r="A107" s="14" t="inlineStr">
         <is>
           <t>Implementación</t>
         </is>
       </c>
-      <c r="B90" s="4" t="inlineStr">
+      <c r="B107" s="4" t="inlineStr">
         <is>
           <t>N=100
 Avg (ms)</t>
         </is>
       </c>
-      <c r="C90" s="4" t="inlineStr">
+      <c r="C107" s="4" t="inlineStr">
         <is>
           <t>N=100
 Speedup</t>
         </is>
       </c>
-      <c r="D90" s="4" t="inlineStr">
+      <c r="D107" s="4" t="inlineStr">
         <is>
           <t>N=200
 Avg (ms)</t>
         </is>
       </c>
-      <c r="E90" s="4" t="inlineStr">
+      <c r="E107" s="4" t="inlineStr">
         <is>
           <t>N=200
 Speedup</t>
         </is>
       </c>
-      <c r="F90" s="4" t="inlineStr">
+      <c r="F107" s="4" t="inlineStr">
         <is>
           <t>N=500
 Avg (ms)</t>
         </is>
       </c>
-      <c r="G90" s="4" t="inlineStr">
+      <c r="G107" s="4" t="inlineStr">
         <is>
           <t>N=500
 Speedup</t>
         </is>
       </c>
-      <c r="H90" s="4" t="inlineStr">
+      <c r="H107" s="4" t="inlineStr">
         <is>
           <t>N=1K
 Avg (ms)</t>
         </is>
       </c>
-      <c r="I90" s="4" t="inlineStr">
+      <c r="I107" s="4" t="inlineStr">
         <is>
           <t>N=1K
 Speedup</t>
         </is>
       </c>
-      <c r="J90" s="4" t="inlineStr">
+      <c r="J107" s="4" t="inlineStr">
         <is>
           <t>N=2K
 Avg (ms)</t>
         </is>
       </c>
-      <c r="K90" s="4" t="inlineStr">
+      <c r="K107" s="4" t="inlineStr">
         <is>
           <t>N=2K
 Speedup</t>
         </is>
       </c>
-      <c r="L90" s="15" t="inlineStr">
+      <c r="L107" s="15" t="inlineStr">
         <is>
           <t>Speedup
 Prom.</t>
         </is>
       </c>
     </row>
-    <row r="91" ht="17" customHeight="1">
-      <c r="A91" s="16" t="inlineStr">
+    <row r="108" ht="17" customHeight="1">
+      <c r="A108" s="16" t="inlineStr">
         <is>
           <t>Secuencial estándar</t>
         </is>
       </c>
-      <c r="B91" s="17" t="n">
+      <c r="B108" s="17" t="n">
         <v>13.474</v>
       </c>
-      <c r="C91" s="18" t="n">
+      <c r="C108" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="D91" s="17" t="n">
+      <c r="D108" s="17" t="n">
         <v>105.373</v>
       </c>
-      <c r="E91" s="18" t="n">
+      <c r="E108" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="F91" s="17" t="n">
+      <c r="F108" s="17" t="n">
         <v>1609.552</v>
       </c>
-      <c r="G91" s="18" t="n">
+      <c r="G108" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="H91" s="17" t="n">
+      <c r="H108" s="17" t="n">
         <v>12799.818</v>
       </c>
-      <c r="I91" s="18" t="n">
+      <c r="I108" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="J91" s="17" t="n">
+      <c r="J108" s="17" t="n">
         <v>102347.979</v>
       </c>
-      <c r="K91" s="18" t="n">
+      <c r="K108" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="L91" s="19" t="n">
+      <c r="L108" s="19" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="92" ht="17" customHeight="1">
-      <c r="A92" s="16" t="inlineStr">
+    <row r="109" ht="17" customHeight="1">
+      <c r="A109" s="16" t="inlineStr">
         <is>
           <t>Procesos fork (2 procesos)</t>
         </is>
       </c>
-      <c r="B92" s="20" t="n">
+      <c r="B109" s="20" t="n">
         <v>154.547</v>
       </c>
-      <c r="C92" s="18" t="n">
+      <c r="C109" s="18" t="n">
         <v>0.0872</v>
       </c>
-      <c r="D92" s="20" t="n">
+      <c r="D109" s="20" t="n">
         <v>635.384</v>
       </c>
-      <c r="E92" s="18" t="n">
+      <c r="E109" s="18" t="n">
         <v>0.1658</v>
       </c>
-      <c r="F92" s="20" t="n">
+      <c r="F109" s="20" t="n">
         <v>4922.376</v>
       </c>
-      <c r="G92" s="18" t="n">
+      <c r="G109" s="18" t="n">
         <v>0.327</v>
       </c>
-      <c r="H92" s="20" t="n">
+      <c r="H109" s="20" t="n">
         <v>24189.658</v>
       </c>
-      <c r="I92" s="18" t="n">
+      <c r="I109" s="18" t="n">
         <v>0.5291</v>
       </c>
-      <c r="J92" s="20" t="n">
+      <c r="J109" s="20" t="n">
         <v>137611.603</v>
       </c>
-      <c r="K92" s="18" t="n">
+      <c r="K109" s="18" t="n">
         <v>0.7437</v>
       </c>
-      <c r="L92" s="19">
-        <f>IFERROR(AVERAGE(C92,E92,G92,I92,K92),"N/A")</f>
+      <c r="L109" s="19">
+        <f>IFERROR(AVERAGE(C109,E109,G109,I109,K109),"N/A")</f>
         <v/>
       </c>
     </row>
-    <row r="93" ht="17" customHeight="1">
-      <c r="A93" s="16" t="inlineStr">
+    <row r="110" ht="17" customHeight="1">
+      <c r="A110" s="16" t="inlineStr">
         <is>
           <t>Procesos fork (4 procesos)</t>
         </is>
       </c>
-      <c r="B93" s="17" t="n">
+      <c r="B110" s="17" t="n">
         <v>293.129</v>
       </c>
-      <c r="C93" s="18" t="n">
+      <c r="C110" s="18" t="n">
         <v>0.046</v>
       </c>
-      <c r="D93" s="17" t="n">
+      <c r="D110" s="17" t="n">
         <v>951.397</v>
       </c>
-      <c r="E93" s="18" t="n">
+      <c r="E110" s="18" t="n">
         <v>0.1108</v>
       </c>
-      <c r="F93" s="17" t="n">
+      <c r="F110" s="17" t="n">
         <v>21972.025</v>
       </c>
-      <c r="G93" s="18" t="n">
+      <c r="G110" s="18" t="n">
         <v>0.0733</v>
       </c>
-      <c r="H93" s="17" t="n">
+      <c r="H110" s="17" t="n">
         <v>25786.619</v>
       </c>
-      <c r="I93" s="18" t="n">
+      <c r="I110" s="18" t="n">
         <v>0.4964</v>
       </c>
-      <c r="J93" s="17" t="n">
+      <c r="J110" s="17" t="n">
         <v>138087.194</v>
       </c>
-      <c r="K93" s="18" t="n">
+      <c r="K110" s="18" t="n">
         <v>0.7412</v>
       </c>
-      <c r="L93" s="19">
-        <f>IFERROR(AVERAGE(C93,E93,G93,I93,K93),"N/A")</f>
+      <c r="L110" s="19">
+        <f>IFERROR(AVERAGE(C110,E110,G110,I110,K110),"N/A")</f>
         <v/>
       </c>
     </row>
-    <row r="94" ht="17" customHeight="1">
-      <c r="A94" s="16" t="inlineStr">
+    <row r="111" ht="17" customHeight="1">
+      <c r="A111" s="16" t="inlineStr">
         <is>
           <t>Procesos fork (6 procesos)</t>
         </is>
       </c>
-      <c r="B94" s="20" t="n">
-        <v>294.936</v>
-      </c>
-      <c r="C94" s="18" t="n">
-        <v>0.0457</v>
-      </c>
-      <c r="D94" s="20" t="n">
-        <v>1195.328</v>
-      </c>
-      <c r="E94" s="18" t="n">
-        <v>0.0882</v>
-      </c>
-      <c r="F94" s="20" t="n">
-        <v>11220.918</v>
-      </c>
-      <c r="G94" s="18" t="n">
-        <v>0.1434</v>
-      </c>
-      <c r="H94" s="20" t="n">
-        <v>66772.91800000001</v>
-      </c>
-      <c r="I94" s="18" t="n">
-        <v>0.1917</v>
-      </c>
-      <c r="J94" s="20" t="n">
-        <v>137806.737</v>
-      </c>
-      <c r="K94" s="18" t="n">
-        <v>0.7427</v>
-      </c>
-      <c r="L94" s="19">
-        <f>IFERROR(AVERAGE(C94,E94,G94,I94,K94),"N/A")</f>
+      <c r="B111" s="20" t="n">
+        <v>262.726</v>
+      </c>
+      <c r="C111" s="18" t="n">
+        <v>0.0513</v>
+      </c>
+      <c r="D111" s="20" t="n">
+        <v>1088.649</v>
+      </c>
+      <c r="E111" s="18" t="n">
+        <v>0.0968</v>
+      </c>
+      <c r="F111" s="20" t="n">
+        <v>10602.767</v>
+      </c>
+      <c r="G111" s="18" t="n">
+        <v>0.1518</v>
+      </c>
+      <c r="H111" s="20" t="n">
+        <v>53410.254</v>
+      </c>
+      <c r="I111" s="18" t="n">
+        <v>0.2397</v>
+      </c>
+      <c r="J111" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K111" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L111" s="19">
+        <f>IFERROR(AVERAGE(C111,E111,G111,I111,K111),"N/A")</f>
         <v/>
       </c>
     </row>
-    <row r="95" ht="17" customHeight="1">
-      <c r="A95" s="16" t="inlineStr">
+    <row r="112" ht="17" customHeight="1">
+      <c r="A112" s="16" t="inlineStr">
         <is>
           <t>Procesos fork (8 procesos)</t>
         </is>
       </c>
-      <c r="B95" s="17" t="n">
-        <v>294.13</v>
-      </c>
-      <c r="C95" s="18" t="n">
-        <v>0.0458</v>
-      </c>
-      <c r="D95" s="17" t="n">
-        <v>1180.255</v>
-      </c>
-      <c r="E95" s="18" t="n">
-        <v>0.0893</v>
-      </c>
-      <c r="F95" s="17" t="n">
-        <v>11215.543</v>
-      </c>
-      <c r="G95" s="18" t="n">
-        <v>0.1435</v>
-      </c>
-      <c r="H95" s="17" t="n">
-        <v>66773.171</v>
-      </c>
-      <c r="I95" s="18" t="n">
-        <v>0.1917</v>
-      </c>
-      <c r="J95" s="17" t="n">
-        <v>137810.647</v>
-      </c>
-      <c r="K95" s="18" t="n">
-        <v>0.7427</v>
-      </c>
-      <c r="L95" s="19">
-        <f>IFERROR(AVERAGE(C95,E95,G95,I95,K95),"N/A")</f>
+      <c r="B112" s="17" t="n">
+        <v>490.267</v>
+      </c>
+      <c r="C112" s="18" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="D112" s="17" t="n">
+        <v>2143.243</v>
+      </c>
+      <c r="E112" s="18" t="n">
+        <v>0.0492</v>
+      </c>
+      <c r="F112" s="17" t="n">
+        <v>17104.361</v>
+      </c>
+      <c r="G112" s="18" t="n">
+        <v>0.0941</v>
+      </c>
+      <c r="H112" s="17" t="n">
+        <v>96774.93399999999</v>
+      </c>
+      <c r="I112" s="18" t="n">
+        <v>0.1323</v>
+      </c>
+      <c r="J112" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K112" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L112" s="19">
+        <f>IFERROR(AVERAGE(C112,E112,G112,I112,K112),"N/A")</f>
         <v/>
       </c>
     </row>
+    <row r="113" ht="17" customHeight="1">
+      <c r="A113" s="16" t="inlineStr">
+        <is>
+          <t>Procesos fork (12 procesos)</t>
+        </is>
+      </c>
+      <c r="B113" s="20" t="n">
+        <v>770.85</v>
+      </c>
+      <c r="C113" s="18" t="n">
+        <v>0.0175</v>
+      </c>
+      <c r="D113" s="20" t="n">
+        <v>3107.166</v>
+      </c>
+      <c r="E113" s="18" t="n">
+        <v>0.0339</v>
+      </c>
+      <c r="F113" s="20" t="n">
+        <v>23631.67</v>
+      </c>
+      <c r="G113" s="18" t="n">
+        <v>0.06809999999999999</v>
+      </c>
+      <c r="H113" s="20" t="n">
+        <v>118163.735</v>
+      </c>
+      <c r="I113" s="18" t="n">
+        <v>0.1083</v>
+      </c>
+      <c r="J113" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K113" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L113" s="19">
+        <f>IFERROR(AVERAGE(C113,E113,G113,I113,K113),"N/A")</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A54:F54"/>
     <mergeCell ref="A71:F71"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A37:F37"/>
-    <mergeCell ref="A89:L89"/>
+    <mergeCell ref="A106:L106"/>
+    <mergeCell ref="A88:F88"/>
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="A20:F20"/>
   </mergeCells>
@@ -6721,32 +7047,32 @@
           <t>p</t>
         </is>
       </c>
-      <c r="B3" s="23" t="inlineStr">
+      <c r="B3" s="24" t="inlineStr">
         <is>
           <t>Hilos (ms)</t>
         </is>
       </c>
-      <c r="C3" s="23" t="inlineStr">
+      <c r="C3" s="24" t="inlineStr">
         <is>
           <t>Hilos sp</t>
         </is>
       </c>
-      <c r="D3" s="23" t="inlineStr">
+      <c r="D3" s="24" t="inlineStr">
         <is>
           <t>Hilos iters</t>
         </is>
       </c>
-      <c r="E3" s="24" t="inlineStr">
+      <c r="E3" s="25" t="inlineStr">
         <is>
           <t>Procesos (ms)</t>
         </is>
       </c>
-      <c r="F3" s="24" t="inlineStr">
+      <c r="F3" s="25" t="inlineStr">
         <is>
           <t>Procesos sp</t>
         </is>
       </c>
-      <c r="G3" s="24" t="inlineStr">
+      <c r="G3" s="25" t="inlineStr">
         <is>
           <t>Procesos iters</t>
         </is>
@@ -6756,22 +7082,22 @@
       <c r="A4" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="25" t="n">
+      <c r="B4" s="26" t="n">
         <v>157.4619</v>
       </c>
       <c r="C4" s="18" t="n">
         <v>0.0856</v>
       </c>
-      <c r="D4" s="26" t="n">
+      <c r="D4" s="27" t="n">
         <v>30849</v>
       </c>
-      <c r="E4" s="27" t="n">
+      <c r="E4" s="28" t="n">
         <v>154.5467</v>
       </c>
-      <c r="F4" s="28" t="n">
+      <c r="F4" s="29" t="n">
         <v>0.0872</v>
       </c>
-      <c r="G4" s="29" t="n">
+      <c r="G4" s="30" t="n">
         <v>30849</v>
       </c>
     </row>
@@ -6779,22 +7105,22 @@
       <c r="A5" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="25" t="n">
+      <c r="B5" s="26" t="n">
         <v>176.3959</v>
       </c>
       <c r="C5" s="18" t="n">
         <v>0.0764</v>
       </c>
-      <c r="D5" s="26" t="n">
+      <c r="D5" s="27" t="n">
         <v>30849</v>
       </c>
-      <c r="E5" s="27" t="n">
+      <c r="E5" s="28" t="n">
         <v>293.1286</v>
       </c>
-      <c r="F5" s="28" t="n">
+      <c r="F5" s="29" t="n">
         <v>0.046</v>
       </c>
-      <c r="G5" s="29" t="n">
+      <c r="G5" s="30" t="n">
         <v>57136</v>
       </c>
     </row>
@@ -6802,75 +7128,69 @@
       <c r="A6" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="B6" s="25" t="n">
+      <c r="B6" s="26" t="n">
         <v>185.2469</v>
       </c>
       <c r="C6" s="18" t="n">
         <v>0.0727</v>
       </c>
-      <c r="D6" s="26" t="n">
+      <c r="D6" s="27" t="n">
         <v>30849</v>
       </c>
-      <c r="E6" s="27" t="n">
-        <v>294.936</v>
-      </c>
-      <c r="F6" s="28" t="n">
-        <v>0.0457</v>
-      </c>
-      <c r="G6" s="29" t="n">
-        <v>72093</v>
+      <c r="E6" s="28" t="n">
+        <v>262.7264</v>
+      </c>
+      <c r="F6" s="29" t="n">
+        <v>0.0513</v>
+      </c>
+      <c r="G6" s="30" t="n">
+        <v>70733</v>
       </c>
     </row>
     <row r="7" ht="16" customHeight="1">
       <c r="A7" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="B7" s="25" t="n">
+      <c r="B7" s="26" t="n">
         <v>369.5485</v>
       </c>
       <c r="C7" s="18" t="n">
         <v>0.0365</v>
       </c>
-      <c r="D7" s="26" t="n">
+      <c r="D7" s="27" t="n">
         <v>30849</v>
       </c>
-      <c r="E7" s="27" t="n">
-        <v>294.13</v>
-      </c>
-      <c r="F7" s="28" t="n">
-        <v>0.0458</v>
-      </c>
-      <c r="G7" s="29" t="n">
-        <v>72093</v>
+      <c r="E7" s="28" t="n">
+        <v>490.2671</v>
+      </c>
+      <c r="F7" s="29" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="G7" s="30" t="n">
+        <v>71747</v>
       </c>
     </row>
     <row r="8" ht="16" customHeight="1">
       <c r="A8" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="B8" s="25" t="n">
+      <c r="B8" s="26" t="n">
         <v>529.3345</v>
       </c>
       <c r="C8" s="18" t="n">
         <v>0.0255</v>
       </c>
-      <c r="D8" s="26" t="n">
+      <c r="D8" s="27" t="n">
         <v>30849</v>
       </c>
-      <c r="E8" s="30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="E8" s="28" t="n">
+        <v>770.8496</v>
+      </c>
+      <c r="F8" s="29" t="n">
+        <v>0.0175</v>
+      </c>
+      <c r="G8" s="30" t="n">
+        <v>76108</v>
       </c>
     </row>
     <row r="9" ht="8" customHeight="1">
@@ -6895,32 +7215,32 @@
           <t>p</t>
         </is>
       </c>
-      <c r="B11" s="23" t="inlineStr">
+      <c r="B11" s="24" t="inlineStr">
         <is>
           <t>Hilos (ms)</t>
         </is>
       </c>
-      <c r="C11" s="23" t="inlineStr">
+      <c r="C11" s="24" t="inlineStr">
         <is>
           <t>Hilos sp</t>
         </is>
       </c>
-      <c r="D11" s="23" t="inlineStr">
+      <c r="D11" s="24" t="inlineStr">
         <is>
           <t>Hilos iters</t>
         </is>
       </c>
-      <c r="E11" s="24" t="inlineStr">
+      <c r="E11" s="25" t="inlineStr">
         <is>
           <t>Procesos (ms)</t>
         </is>
       </c>
-      <c r="F11" s="24" t="inlineStr">
+      <c r="F11" s="25" t="inlineStr">
         <is>
           <t>Procesos sp</t>
         </is>
       </c>
-      <c r="G11" s="24" t="inlineStr">
+      <c r="G11" s="25" t="inlineStr">
         <is>
           <t>Procesos iters</t>
         </is>
@@ -6930,22 +7250,22 @@
       <c r="A12" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B12" s="25" t="n">
+      <c r="B12" s="26" t="n">
         <v>701.9948000000001</v>
       </c>
       <c r="C12" s="18" t="n">
         <v>0.1501</v>
       </c>
-      <c r="D12" s="26" t="n">
+      <c r="D12" s="27" t="n">
         <v>122171</v>
       </c>
-      <c r="E12" s="27" t="n">
+      <c r="E12" s="28" t="n">
         <v>635.3838</v>
       </c>
-      <c r="F12" s="28" t="n">
+      <c r="F12" s="29" t="n">
         <v>0.1658</v>
       </c>
-      <c r="G12" s="29" t="n">
+      <c r="G12" s="30" t="n">
         <v>122171</v>
       </c>
     </row>
@@ -6953,22 +7273,22 @@
       <c r="A13" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="B13" s="25" t="n">
+      <c r="B13" s="26" t="n">
         <v>728.4643</v>
       </c>
       <c r="C13" s="18" t="n">
         <v>0.1447</v>
       </c>
-      <c r="D13" s="26" t="n">
+      <c r="D13" s="27" t="n">
         <v>122171</v>
       </c>
-      <c r="E13" s="27" t="n">
+      <c r="E13" s="28" t="n">
         <v>951.3964999999999</v>
       </c>
-      <c r="F13" s="28" t="n">
+      <c r="F13" s="29" t="n">
         <v>0.1108</v>
       </c>
-      <c r="G13" s="29" t="n">
+      <c r="G13" s="30" t="n">
         <v>171041</v>
       </c>
     </row>
@@ -6976,75 +7296,69 @@
       <c r="A14" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="B14" s="25" t="n">
+      <c r="B14" s="26" t="n">
         <v>765.8803</v>
       </c>
       <c r="C14" s="18" t="n">
         <v>0.1376</v>
       </c>
-      <c r="D14" s="26" t="n">
+      <c r="D14" s="27" t="n">
         <v>122171</v>
       </c>
-      <c r="E14" s="27" t="n">
-        <v>1195.328</v>
-      </c>
-      <c r="F14" s="28" t="n">
-        <v>0.0882</v>
-      </c>
-      <c r="G14" s="29" t="n">
-        <v>305050</v>
+      <c r="E14" s="28" t="n">
+        <v>1088.6493</v>
+      </c>
+      <c r="F14" s="29" t="n">
+        <v>0.0968</v>
+      </c>
+      <c r="G14" s="30" t="n">
+        <v>300590</v>
       </c>
     </row>
     <row r="15" ht="16" customHeight="1">
       <c r="A15" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="B15" s="25" t="n">
+      <c r="B15" s="26" t="n">
         <v>1481.9257</v>
       </c>
       <c r="C15" s="18" t="n">
         <v>0.0711</v>
       </c>
-      <c r="D15" s="26" t="n">
+      <c r="D15" s="27" t="n">
         <v>122171</v>
       </c>
-      <c r="E15" s="27" t="n">
-        <v>1180.2555</v>
-      </c>
-      <c r="F15" s="28" t="n">
-        <v>0.0893</v>
-      </c>
-      <c r="G15" s="29" t="n">
-        <v>305050</v>
+      <c r="E15" s="28" t="n">
+        <v>2143.243</v>
+      </c>
+      <c r="F15" s="29" t="n">
+        <v>0.0492</v>
+      </c>
+      <c r="G15" s="30" t="n">
+        <v>310660</v>
       </c>
     </row>
     <row r="16" ht="16" customHeight="1">
       <c r="A16" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="25" t="n">
+      <c r="B16" s="26" t="n">
         <v>2109.0962</v>
       </c>
       <c r="C16" s="18" t="n">
         <v>0.05</v>
       </c>
-      <c r="D16" s="26" t="n">
+      <c r="D16" s="27" t="n">
         <v>122171</v>
       </c>
-      <c r="E16" s="30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F16" s="30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G16" s="30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="E16" s="28" t="n">
+        <v>3107.1656</v>
+      </c>
+      <c r="F16" s="29" t="n">
+        <v>0.0339</v>
+      </c>
+      <c r="G16" s="30" t="n">
+        <v>303976</v>
       </c>
     </row>
     <row r="17" ht="8" customHeight="1">
@@ -7069,32 +7383,32 @@
           <t>p</t>
         </is>
       </c>
-      <c r="B19" s="23" t="inlineStr">
+      <c r="B19" s="24" t="inlineStr">
         <is>
           <t>Hilos (ms)</t>
         </is>
       </c>
-      <c r="C19" s="23" t="inlineStr">
+      <c r="C19" s="24" t="inlineStr">
         <is>
           <t>Hilos sp</t>
         </is>
       </c>
-      <c r="D19" s="23" t="inlineStr">
+      <c r="D19" s="24" t="inlineStr">
         <is>
           <t>Hilos iters</t>
         </is>
       </c>
-      <c r="E19" s="24" t="inlineStr">
+      <c r="E19" s="25" t="inlineStr">
         <is>
           <t>Procesos (ms)</t>
         </is>
       </c>
-      <c r="F19" s="24" t="inlineStr">
+      <c r="F19" s="25" t="inlineStr">
         <is>
           <t>Procesos sp</t>
         </is>
       </c>
-      <c r="G19" s="24" t="inlineStr">
+      <c r="G19" s="25" t="inlineStr">
         <is>
           <t>Procesos iters</t>
         </is>
@@ -7104,22 +7418,22 @@
       <c r="A20" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B20" s="25" t="n">
+      <c r="B20" s="26" t="n">
         <v>5361.9059</v>
       </c>
       <c r="C20" s="18" t="n">
         <v>0.3002</v>
       </c>
-      <c r="D20" s="26" t="n">
+      <c r="D20" s="27" t="n">
         <v>758964</v>
       </c>
-      <c r="E20" s="27" t="n">
+      <c r="E20" s="28" t="n">
         <v>4922.3756</v>
       </c>
-      <c r="F20" s="28" t="n">
+      <c r="F20" s="29" t="n">
         <v>0.327</v>
       </c>
-      <c r="G20" s="29" t="n">
+      <c r="G20" s="30" t="n">
         <v>758964</v>
       </c>
     </row>
@@ -7127,22 +7441,22 @@
       <c r="A21" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="B21" s="25" t="n">
+      <c r="B21" s="26" t="n">
         <v>5430.4177</v>
       </c>
       <c r="C21" s="18" t="n">
         <v>0.2964</v>
       </c>
-      <c r="D21" s="26" t="n">
+      <c r="D21" s="27" t="n">
         <v>758964</v>
       </c>
-      <c r="E21" s="27" t="n">
+      <c r="E21" s="28" t="n">
         <v>21972.0252</v>
       </c>
-      <c r="F21" s="28" t="n">
+      <c r="F21" s="29" t="n">
         <v>0.0733</v>
       </c>
-      <c r="G21" s="29" t="n">
+      <c r="G21" s="30" t="n">
         <v>3377076</v>
       </c>
     </row>
@@ -7150,75 +7464,69 @@
       <c r="A22" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="B22" s="25" t="n">
+      <c r="B22" s="26" t="n">
         <v>5634.4252</v>
       </c>
       <c r="C22" s="18" t="n">
         <v>0.2857</v>
       </c>
-      <c r="D22" s="26" t="n">
+      <c r="D22" s="27" t="n">
         <v>758964</v>
       </c>
-      <c r="E22" s="27" t="n">
-        <v>11220.918</v>
-      </c>
-      <c r="F22" s="28" t="n">
-        <v>0.1434</v>
-      </c>
-      <c r="G22" s="29" t="n">
-        <v>2479060</v>
+      <c r="E22" s="28" t="n">
+        <v>10602.7674</v>
+      </c>
+      <c r="F22" s="29" t="n">
+        <v>0.1518</v>
+      </c>
+      <c r="G22" s="30" t="n">
+        <v>2573935</v>
       </c>
     </row>
     <row r="23" ht="16" customHeight="1">
       <c r="A23" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="B23" s="25" t="n">
+      <c r="B23" s="26" t="n">
         <v>9785.354799999999</v>
       </c>
       <c r="C23" s="18" t="n">
         <v>0.1645</v>
       </c>
-      <c r="D23" s="26" t="n">
+      <c r="D23" s="27" t="n">
         <v>758964</v>
       </c>
-      <c r="E23" s="27" t="n">
-        <v>11215.5433</v>
-      </c>
-      <c r="F23" s="28" t="n">
-        <v>0.1435</v>
-      </c>
-      <c r="G23" s="29" t="n">
-        <v>2479060</v>
+      <c r="E23" s="28" t="n">
+        <v>17104.3605</v>
+      </c>
+      <c r="F23" s="29" t="n">
+        <v>0.0941</v>
+      </c>
+      <c r="G23" s="30" t="n">
+        <v>2317058</v>
       </c>
     </row>
     <row r="24" ht="16" customHeight="1">
       <c r="A24" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="B24" s="25" t="n">
+      <c r="B24" s="26" t="n">
         <v>13440.5995</v>
       </c>
       <c r="C24" s="18" t="n">
         <v>0.1198</v>
       </c>
-      <c r="D24" s="26" t="n">
+      <c r="D24" s="27" t="n">
         <v>758964</v>
       </c>
-      <c r="E24" s="30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F24" s="30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G24" s="30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="E24" s="28" t="n">
+        <v>23631.67</v>
+      </c>
+      <c r="F24" s="29" t="n">
+        <v>0.06809999999999999</v>
+      </c>
+      <c r="G24" s="30" t="n">
+        <v>2185791</v>
       </c>
     </row>
     <row r="25" ht="8" customHeight="1">
@@ -7243,32 +7551,32 @@
           <t>p</t>
         </is>
       </c>
-      <c r="B27" s="23" t="inlineStr">
+      <c r="B27" s="24" t="inlineStr">
         <is>
           <t>Hilos (ms)</t>
         </is>
       </c>
-      <c r="C27" s="23" t="inlineStr">
+      <c r="C27" s="24" t="inlineStr">
         <is>
           <t>Hilos sp</t>
         </is>
       </c>
-      <c r="D27" s="23" t="inlineStr">
+      <c r="D27" s="24" t="inlineStr">
         <is>
           <t>Hilos iters</t>
         </is>
       </c>
-      <c r="E27" s="24" t="inlineStr">
+      <c r="E27" s="25" t="inlineStr">
         <is>
           <t>Procesos (ms)</t>
         </is>
       </c>
-      <c r="F27" s="24" t="inlineStr">
+      <c r="F27" s="25" t="inlineStr">
         <is>
           <t>Procesos sp</t>
         </is>
       </c>
-      <c r="G27" s="24" t="inlineStr">
+      <c r="G27" s="25" t="inlineStr">
         <is>
           <t>Procesos iters</t>
         </is>
@@ -7278,22 +7586,22 @@
       <c r="A28" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B28" s="25" t="n">
+      <c r="B28" s="26" t="n">
         <v>27078.0804</v>
       </c>
       <c r="C28" s="18" t="n">
         <v>0.4727</v>
       </c>
-      <c r="D28" s="26" t="n">
+      <c r="D28" s="27" t="n">
         <v>3029711</v>
       </c>
-      <c r="E28" s="27" t="n">
+      <c r="E28" s="28" t="n">
         <v>24189.6581</v>
       </c>
-      <c r="F28" s="28" t="n">
+      <c r="F28" s="29" t="n">
         <v>0.5291</v>
       </c>
-      <c r="G28" s="29" t="n">
+      <c r="G28" s="30" t="n">
         <v>3029711</v>
       </c>
     </row>
@@ -7301,22 +7609,22 @@
       <c r="A29" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="B29" s="25" t="n">
+      <c r="B29" s="26" t="n">
         <v>26977.8137</v>
       </c>
       <c r="C29" s="18" t="n">
         <v>0.4745</v>
       </c>
-      <c r="D29" s="26" t="n">
+      <c r="D29" s="27" t="n">
         <v>3029711</v>
       </c>
-      <c r="E29" s="27" t="n">
+      <c r="E29" s="28" t="n">
         <v>25786.6187</v>
       </c>
-      <c r="F29" s="28" t="n">
+      <c r="F29" s="29" t="n">
         <v>0.4964</v>
       </c>
-      <c r="G29" s="29" t="n">
+      <c r="G29" s="30" t="n">
         <v>3174419</v>
       </c>
     </row>
@@ -7324,75 +7632,69 @@
       <c r="A30" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="B30" s="25" t="n">
+      <c r="B30" s="26" t="n">
         <v>26301.5481</v>
       </c>
       <c r="C30" s="18" t="n">
         <v>0.4867</v>
       </c>
-      <c r="D30" s="26" t="n">
+      <c r="D30" s="27" t="n">
         <v>3029711</v>
       </c>
-      <c r="E30" s="27" t="n">
-        <v>66772.91800000001</v>
-      </c>
-      <c r="F30" s="28" t="n">
-        <v>0.1917</v>
-      </c>
-      <c r="G30" s="29" t="n">
-        <v>7904234</v>
+      <c r="E30" s="28" t="n">
+        <v>53410.2537</v>
+      </c>
+      <c r="F30" s="29" t="n">
+        <v>0.2397</v>
+      </c>
+      <c r="G30" s="30" t="n">
+        <v>6751089</v>
       </c>
     </row>
     <row r="31" ht="16" customHeight="1">
       <c r="A31" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="B31" s="25" t="n">
+      <c r="B31" s="26" t="n">
         <v>42068.9988</v>
       </c>
       <c r="C31" s="18" t="n">
         <v>0.3043</v>
       </c>
-      <c r="D31" s="26" t="n">
+      <c r="D31" s="27" t="n">
         <v>3029711</v>
       </c>
-      <c r="E31" s="27" t="n">
-        <v>66773.17049999999</v>
-      </c>
-      <c r="F31" s="28" t="n">
-        <v>0.1917</v>
-      </c>
-      <c r="G31" s="29" t="n">
-        <v>7904234</v>
+      <c r="E31" s="28" t="n">
+        <v>96774.9336</v>
+      </c>
+      <c r="F31" s="29" t="n">
+        <v>0.1323</v>
+      </c>
+      <c r="G31" s="30" t="n">
+        <v>11664547</v>
       </c>
     </row>
     <row r="32" ht="16" customHeight="1">
       <c r="A32" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="B32" s="25" t="n">
+      <c r="B32" s="26" t="n">
         <v>56774.7003</v>
       </c>
       <c r="C32" s="18" t="n">
         <v>0.2254</v>
       </c>
-      <c r="D32" s="26" t="n">
+      <c r="D32" s="27" t="n">
         <v>3029711</v>
       </c>
-      <c r="E32" s="30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F32" s="30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G32" s="30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="E32" s="28" t="n">
+        <v>118163.7355</v>
+      </c>
+      <c r="F32" s="29" t="n">
+        <v>0.1083</v>
+      </c>
+      <c r="G32" s="30" t="n">
+        <v>9777002</v>
       </c>
     </row>
     <row r="33" ht="8" customHeight="1">
@@ -7417,32 +7719,32 @@
           <t>p</t>
         </is>
       </c>
-      <c r="B35" s="23" t="inlineStr">
+      <c r="B35" s="24" t="inlineStr">
         <is>
           <t>Hilos (ms)</t>
         </is>
       </c>
-      <c r="C35" s="23" t="inlineStr">
+      <c r="C35" s="24" t="inlineStr">
         <is>
           <t>Hilos sp</t>
         </is>
       </c>
-      <c r="D35" s="23" t="inlineStr">
+      <c r="D35" s="24" t="inlineStr">
         <is>
           <t>Hilos iters</t>
         </is>
       </c>
-      <c r="E35" s="24" t="inlineStr">
+      <c r="E35" s="25" t="inlineStr">
         <is>
           <t>Procesos (ms)</t>
         </is>
       </c>
-      <c r="F35" s="24" t="inlineStr">
+      <c r="F35" s="25" t="inlineStr">
         <is>
           <t>Procesos sp</t>
         </is>
       </c>
-      <c r="G35" s="24" t="inlineStr">
+      <c r="G35" s="25" t="inlineStr">
         <is>
           <t>Procesos iters</t>
         </is>
@@ -7452,22 +7754,22 @@
       <c r="A36" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B36" s="25" t="n">
+      <c r="B36" s="26" t="n">
         <v>153161.5799</v>
       </c>
       <c r="C36" s="18" t="n">
         <v>0.6682</v>
       </c>
-      <c r="D36" s="26" t="n">
+      <c r="D36" s="27" t="n">
         <v>12106565</v>
       </c>
-      <c r="E36" s="27" t="n">
+      <c r="E36" s="28" t="n">
         <v>137611.603</v>
       </c>
-      <c r="F36" s="28" t="n">
+      <c r="F36" s="29" t="n">
         <v>0.7437</v>
       </c>
-      <c r="G36" s="29" t="n">
+      <c r="G36" s="30" t="n">
         <v>12106565</v>
       </c>
     </row>
@@ -7475,22 +7777,22 @@
       <c r="A37" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="B37" s="25" t="n">
+      <c r="B37" s="26" t="n">
         <v>147359.8108</v>
       </c>
       <c r="C37" s="18" t="n">
         <v>0.6945</v>
       </c>
-      <c r="D37" s="26" t="n">
+      <c r="D37" s="27" t="n">
         <v>12106565</v>
       </c>
-      <c r="E37" s="27" t="n">
+      <c r="E37" s="28" t="n">
         <v>138087.1941</v>
       </c>
-      <c r="F37" s="28" t="n">
+      <c r="F37" s="29" t="n">
         <v>0.7412</v>
       </c>
-      <c r="G37" s="29" t="n">
+      <c r="G37" s="30" t="n">
         <v>12148307</v>
       </c>
     </row>
@@ -7498,72 +7800,84 @@
       <c r="A38" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="B38" s="25" t="n">
+      <c r="B38" s="26" t="n">
         <v>141045.8615</v>
       </c>
       <c r="C38" s="18" t="n">
         <v>0.7256</v>
       </c>
-      <c r="D38" s="26" t="n">
+      <c r="D38" s="27" t="n">
         <v>12106565</v>
       </c>
-      <c r="E38" s="27" t="n">
-        <v>137806.737</v>
-      </c>
-      <c r="F38" s="28" t="n">
-        <v>0.7427</v>
-      </c>
-      <c r="G38" s="29" t="n">
-        <v>12127661</v>
+      <c r="E38" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F38" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G38" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="39" ht="16" customHeight="1">
       <c r="A39" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="B39" s="25" t="n">
+      <c r="B39" s="26" t="n">
         <v>181170.8651</v>
       </c>
       <c r="C39" s="18" t="n">
         <v>0.5649</v>
       </c>
-      <c r="D39" s="26" t="n">
+      <c r="D39" s="27" t="n">
         <v>12106565</v>
       </c>
-      <c r="E39" s="27" t="n">
-        <v>137810.647</v>
-      </c>
-      <c r="F39" s="28" t="n">
-        <v>0.7427</v>
-      </c>
-      <c r="G39" s="29" t="n">
-        <v>12127661</v>
+      <c r="E39" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F39" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G39" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="40" ht="16" customHeight="1">
       <c r="A40" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="B40" s="25" t="n">
+      <c r="B40" s="26" t="n">
         <v>263142.2311</v>
       </c>
       <c r="C40" s="18" t="n">
         <v>0.3889</v>
       </c>
-      <c r="D40" s="26" t="n">
+      <c r="D40" s="27" t="n">
         <v>12106565</v>
       </c>
-      <c r="E40" s="30" t="inlineStr">
+      <c r="E40" s="31" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F40" s="30" t="inlineStr">
+      <c r="F40" s="31" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G40" s="30" t="inlineStr">
+      <c r="G40" s="31" t="inlineStr">
         <is>
           <t>—</t>
         </is>
